--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-rand-sf36-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-rand-sf36-answers.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-22T11:57:51+00:00</t>
+    <t>2026-02-25T07:03:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-rand-sf36-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-rand-sf36-answers.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T07:03:20+00:00</t>
+    <t>2026-02-26T10:01:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
